--- a/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D42_r1_Open-actions-and-outstanding-information-registe.xlsx
+++ b/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D42_r1_Open-actions-and-outstanding-information-registe.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document ITT-CONTRACT (Invitation to tender, conditions of contract, BOQ preamble / method of measurement (NOT provided)</t>
+          <t>Resolve query (technical): BOQ item 1.1 ('Excavation in pits for footings') uses open wording (assumed, assumption, confirm, not printed) in: Remar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-ARCH-SET (Architect's drawing set - 'a 16-sheet drawing set' (p.1): ground-floor plan, first-floor plan, ro</t>
+          <t>Resolve query (technical): BOQ item 7.1 ('Roof and canopy members') uses open wording (not stated) in: Section. Please state the exact scope, exten</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-MEP (Mechanical, plumbing, electrical, fire, ELV drawings (NOT provided; not in scope of the source BOQ)) i</t>
+          <t>Resolve query (boq_discrepancy): BOQ items 5.2 and 5.3 are almost identical ('Door 800 × 2400 mm' vs 'Door 802 × 2400 mm'; sizes differ by &lt;= 1%). Are th</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-STR-COLUMN (Structural column keys and column details (items 2.2-2.4; NOT provided)) is required for the te</t>
+          <t>Resolve query (boq_discrepancy): BOQ items 5.16 and 5.20 are almost identical ('Window 1206 × 2000 mm' vs 'Window 1200 × 2000 mm'; sizes differ by &lt;= 1%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-STR-FOOTING (Structural footing layout (basis of item 2.1; NOT provided)) is required for the tender but ha</t>
+          <t>Resolve query (missing_input): Document ITT-CONTRACT (Invitation to tender, conditions of contract, BOQ preamble / method of measurement (NOT provided)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-STR-SLABBEAM (Structural slab/beam sheets and beam details (items 2.5-2.9; NOT provided)) is required for t</t>
+          <t>Resolve query (missing_input): Document DWG-ARCH-SET (Architect's drawing set - 'a 16-sheet drawing set' (p.1): ground-floor plan, first-floor plan, ro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-STR-STAIR (Structural stair sheet - the source says it was 'quarantined' (item 2.10; NOT provided)) is requ</t>
+          <t>Resolve query (missing_input): Document DWG-MEP (Mechanical, plumbing, electrical, fire, ELV drawings (NOT provided; not in scope of the source BOQ)) i</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document BBS-REINF (Reinforcement bar bending schedule - the source says it is excluded (p.7; NOT provided)) is required</t>
+          <t>Resolve query (missing_input): Document DWG-STR-COLUMN (Structural column keys and column details (items 2.2-2.4; NOT provided)) is required for the te</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document SPEC-ARCH (Architectural specification: plaster, door and window schedules, railings (NOT provided)) is require</t>
+          <t>Resolve query (missing_input): Document DWG-STR-FOOTING (Structural footing layout (basis of item 2.1; NOT provided)) is required for the tender but ha</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve query (missing_input): Document SPEC-STRUCT (Structural / concrete / masonry specification (grades, cover, mix; NOT provided)) is required for </t>
+          <t>Resolve query (missing_input): Document DWG-STR-SLABBEAM (Structural slab/beam sheets and beam details (items 2.5-2.9; NOT provided)) is required for t</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Document DWG-SITE-LEVELS (Site survey / natural ground level (item 1.1 assumption; NOT provided)) is required for the te</t>
+          <t>Resolve query (missing_input): Document DWG-STR-STAIR (Structural stair sheet - the source says it was 'quarantined' (item 2.10; NOT provided)) is requ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 11 mandatory assumption(s) in 'Commercial terms and payment' need confirmation of the project basis: ASMP-I-001 Commerci</t>
+          <t>Resolve query (missing_input): Document BBS-REINF (Reinforcement bar bending schedule - the source says it is excluded (p.7; NOT provided)) is required</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 6 mandatory assumption(s) in 'Commissioning, testing and handover' need confirmation of the project basis: ASMP-K-001 In</t>
+          <t>Resolve query (missing_input): Document SPEC-ARCH (Architectural specification: plaster, door and window schedules, railings (NOT provided)) is require</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 2 mandatory assumption(s) in 'Logistics, transport and landed cost' need confirmation of the project basis: ASMP-F-001 D</t>
+          <t xml:space="preserve">Resolve query (missing_input): Document SPEC-STRUCT (Structural / concrete / masonry specification (grades, cover, mix; NOT provided)) is required for </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 6 mandatory assumption(s) in 'Material, labour, plant and equipment rates' need confirmation of the project basis: ASMP-</t>
+          <t>Resolve query (missing_input): Document DWG-SITE-LEVELS (Site survey / natural ground level (item 1.1 assumption; NOT provided)) is required for the te</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 8 mandatory assumption(s) in 'Preliminaries and indirects' need confirmation of the project basis: ASMP-H-001 Indirect c</t>
+          <t>Resolve query (assumption_confirmation): 11 mandatory assumption(s) in 'Commercial terms and payment' need confirmation of the project basis: ASMP-I-001 Commerci</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve query (assumption_confirmation): 9 mandatory assumption(s) in 'Productivity and workforce' need confirmation of the project basis: ASMP-D-001 Paid hours </t>
+          <t>Resolve query (assumption_confirmation): 6 mandatory assumption(s) in 'Commissioning, testing and handover' need confirmation of the project basis: ASMP-K-001 In</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 9 mandatory assumption(s) in 'Quantities and measurement' need confirmation of the project basis: ASMP-B-001 Measurement</t>
+          <t>Resolve query (assumption_confirmation): 2 mandatory assumption(s) in 'Logistics, transport and landed cost' need confirmation of the project basis: ASMP-F-001 D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 8 mandatory assumption(s) in 'Risk and contingency' need confirmation of the project basis: ASMP-L-001 Rate source confi</t>
+          <t>Resolve query (assumption_confirmation): 6 mandatory assumption(s) in 'Material, labour, plant and equipment rates' need confirmation of the project basis: ASMP-</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 16 mandatory assumption(s) in 'Scope and design' need confirmation of the project basis: ASMP-A-001 Design stage of esti</t>
+          <t>Resolve query (assumption_confirmation): 8 mandatory assumption(s) in 'Preliminaries and indirects' need confirmation of the project basis: ASMP-H-001 Indirect c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Resolve query (assumption_confirmation): 10 mandatory assumption(s) in 'Taxes and statutory costs' need confirmation of the project basis: ASMP-J-001 Default tax</t>
+          <t xml:space="preserve">Resolve query (assumption_confirmation): 9 mandatory assumption(s) in 'Productivity and workforce' need confirmation of the project basis: ASMP-D-001 Paid hours </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve query (boq_discrepancy): Item 1.3 'Backfill around footings' (240.58 m3) is printed as 'excavation - footing - blinding'. 314.04 - 55.40 - 18.33 </t>
+          <t>Resolve query (assumption_confirmation): 9 mandatory assumption(s) in 'Quantities and measurement' need confirmation of the project basis: ASMP-B-001 Measurement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resolve query (boq_discrepancy): Page-2 totals differ from the sum of the item lines: RCC 129.42 vs 129.43, formwork 1,746.67 vs 1,746.68, masonry 111.38</t>
+          <t>Resolve query (assumption_confirmation): 8 mandatory assumption(s) in 'Risk and contingency' need confirmation of the project basis: ASMP-L-001 Rate source confi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): Natural ground level is 'not printed - assumed at project +/-0.00'. Please supply the site survey / levels. Items 1.1, 1</t>
+          <t>Resolve query (assumption_confirmation): 16 mandatory assumption(s) in 'Scope and design' need confirmation of the project basis: ASMP-A-001 Design stage of esti</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): The BOQ was measured from a '16-sheet drawing set' (and a 3D model of 434 elements). None of the sheets or the model wer</t>
+          <t>Resolve query (assumption_confirmation): 10 mandatory assumption(s) in 'Taxes and statutory costs' need confirmation of the project basis: ASMP-J-001 Default tax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Resolve query (technical): Item 2.10 RC stairs (4.13 m3): the structural stair sheet is stated as 'quarantined' and the quantity was taken from arc</t>
+          <t xml:space="preserve">Resolve query (boq_discrepancy): Item 1.3 'Backfill around footings' (240.58 m3) is printed as 'excavation - footing - blinding'. 314.04 - 55.40 - 18.33 </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Resolve query (scope_exclusion): Reinforcement steel and its bar bending schedule are excluded from the BOQ. Is steel to be priced by the contractor from</t>
+          <t>Resolve query (boq_discrepancy): Page-2 totals differ from the sum of the item lines: RCC 129.42 vs 129.43, formwork 1,746.67 vs 1,746.68, masonry 111.38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Resolve query (scope_exclusion): Plaster (item 4.4) is measured gross, openings not deducted. Which method of measurement applies to the tender (the docu</t>
+          <t>Resolve query (missing_input): Natural ground level is 'not printed - assumed at project +/-0.00'. Please supply the site survey / levels. Items 1.1, 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Resolve query (scope_exclusion): Flooring, finishes, plumbing, electrical and other services are not in the BOQ ('those come with a full BOQ'). Please co</t>
+          <t>Resolve query (missing_input): The BOQ was measured from a '16-sheet drawing set' (and a 3D model of 434 elements). None of the sheets or the model wer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Resolve query (technical): Openings with unusual sizes: Door 6467x3140, Window 387x3140, Window 368x3140, Window 600x2950, Window 4274x2000. Please</t>
+          <t>Resolve query (technical): Item 2.10 RC stairs (4.13 m3): the structural stair sheet is stated as 'quarantined' and the quantity was taken from arc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Resolve query (boq_discrepancy): Door 900x2400 (7 nos), 800x2400 (4), 802x2400 (1), 736x2400 (1): 802 and 736 look like duplicates/variants of 800. Pleas</t>
+          <t>Resolve query (scope_exclusion): Reinforcement steel and its bar bending schedule are excluded from the BOQ. Is steel to be priced by the contractor from</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Resolve query (missing_input): No specification is supplied: concrete grade, cover and mix, masonry unit type and mortar, plaster thickness/mix, door a</t>
+          <t>Resolve query (scope_exclusion): Plaster (item 4.4) is measured gross, openings not deducted. Which method of measurement applies to the tender (the docu</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Resolve query (technical): The source uses IS 1200 and INR. Which measurement standard, currency, region, tax and contractual basis apply to this e</t>
+          <t>Resolve query (scope_exclusion): Flooring, finishes, plumbing, electrical and other services are not in the BOQ ('those come with a full BOQ'). Please co</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Resolve query (design_interface): Item 7.1 'Roof and canopy members' (48.85 m) gives only a running length. Material (steel/RCC/timber), section, finish a</t>
+          <t>Resolve query (technical): Openings with unusual sizes: Door 6467x3140, Window 387x3140, Window 368x3140, Window 600x2950, Window 4274x2000. Please</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Resolve query (boq_discrepancy): The document says quantities were delivered 6 September 2026 and the page was published 1 October 2026; no revision iden</t>
+          <t>Resolve query (boq_discrepancy): Door 900x2400 (7 nos), 800x2400 (4), 802x2400 (1), 736x2400 (1): 802 and 736 look like duplicates/variants of 800. Pleas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Resolve query (commercial): Rates, amounts and the abstract of cost are blank by design. Which rate basis (DSR, SOR, market) and currency is to be u</t>
+          <t>Resolve query (missing_input): No specification is supplied: concrete grade, cover and mix, masonry unit type and mortar, plaster thickness/mix, door a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1444,100 +1444,100 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-001</t>
+          <t>TQ-PRJ-9201-037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Obtain and register the 16-sheet architectural + structural drawing set; then a person verifies every BOQ quantity against it (0 of 48 lines are verifiable today)</t>
+          <t>Resolve query (technical): The source uses IS 1200 and INR. Which measurement standard, currency, region, tax and contractual basis apply to this e</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Open (due None)</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UNASSIGNED (estimator to assign)</t>
+          <t>Estimator</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-002</t>
+          <t>TQ-PRJ-9201-038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: reinforcement steel (kg) and bar bending schedule - excluded from the source BOQ</t>
+          <t>Resolve query (design_interface): Item 7.1 'Roof and canopy members' (48.85 m) gives only a running length. Material (steel/RCC/timber), section, finish a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Open (due None)</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UNASSIGNED (estimator to assign)</t>
+          <t>Estimator</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-003</t>
+          <t>TQ-PRJ-9201-039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: plaster net area after deducting openings per the method of measurement the customer names</t>
+          <t>Resolve query (boq_discrepancy): The document says quantities were delivered 6 September 2026 and the page was published 1 October 2026; no revision iden</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Open (due None)</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UNASSIGNED (estimator to assign)</t>
+          <t>Estimator</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-004</t>
+          <t>TQ-PRJ-9201-040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: flooring, wall/ceiling finishes, waterproofing, painting, joinery</t>
+          <t>Resolve query (commercial): Rates, amounts and the abstract of cost are blank by design. Which rate basis (DSR, SOR, market) and currency is to be u</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Open (due None)</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UNASSIGNED (estimator to assign)</t>
+          <t>Estimator</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-005</t>
+          <t>ACT-PRJ-9201-001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: plumbing, drainage, electrical, HVAC, fire and ELV quantities</t>
+          <t>Obtain and register the 16-sheet architectural + structural drawing set; then a person verifies every BOQ quantity against it (0 of 48 lines are verifiable today)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1554,12 +1554,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-006</t>
+          <t>ACT-PRJ-9201-002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: external works, boundary wall, gate, site drainage, utilities connections</t>
+          <t>MANUAL TAKEOFF REQUIRED: reinforcement steel (kg) and bar bending schedule - excluded from the source BOQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-007</t>
+          <t>ACT-PRJ-9201-003</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: structural stair - source says the structural stair sheet was quarantined; stair concrete (4.13 m3) was taken from architectural plans</t>
+          <t>MANUAL TAKEOFF REQUIRED: plaster net area after deducting openings per the method of measurement the customer names</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1598,12 +1598,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-008</t>
+          <t>ACT-PRJ-9201-004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Confirm natural ground level; re-measure excavation 1.1, blinding 1.2, backfill 1.3 together if it changes</t>
+          <t>MANUAL TAKEOFF REQUIRED: flooring, wall/ceiling finishes, waterproofing, painting, joinery</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-009</t>
+          <t>ACT-PRJ-9201-005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: roof and canopy member sections/material/weights (only a run length is given)</t>
+          <t>MANUAL TAKEOFF REQUIRED: plumbing, drainage, electrical, HVAC, fire and ELV quantities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ACT-PRJ-9201-010</t>
+          <t>ACT-PRJ-9201-006</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MANUAL TAKEOFF REQUIRED: railing type/height/material and fixings (only a run length is given)</t>
+          <t>MANUAL TAKEOFF REQUIRED: external works, boundary wall, gate, site drainage, utilities connections</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1664,88 +1664,88 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>ACT-PRJ-9201-007</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>the project is flagged as a demonstration project</t>
+          <t>MANUAL TAKEOFF REQUIRED: structural stair - source says the structural stair sheet was quarantined; stair concrete (4.13 m3) was taken from architectural plans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open (due None)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Commercial Approver</t>
+          <t>UNASSIGNED (estimator to assign)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>ACT-PRJ-9201-008</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>the environment is 'test', not 'production'</t>
+          <t>Confirm natural ground level; re-measure excavation 1.1, blinding 1.2, backfill 1.3 together if it changes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open (due None)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Commercial Approver</t>
+          <t>UNASSIGNED (estimator to assign)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>ACT-PRJ-9201-009</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>estimate approval: no approval record</t>
+          <t>MANUAL TAKEOFF REQUIRED: roof and canopy member sections/material/weights (only a run length is given)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open (due None)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Commercial Approver</t>
+          <t>UNASSIGNED (estimator to assign)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>ACT-PRJ-9201-010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>letter of offer: none generated</t>
+          <t>MANUAL TAKEOFF REQUIRED: railing type/height/material and fixings (only a run length is given)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open (due None)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Commercial Approver</t>
+          <t>UNASSIGNED (estimator to assign)</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>tender-export approval: no approval record</t>
+          <t>the project is flagged as a demonstration project</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reconciliation gate blocked by 50 finding(s)</t>
+          <t>the environment is 'test', not 'production'</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>estimate state is 'Preliminary — Incomplete'</t>
+          <t>project region/currency (KSA-ALL / SAR) are system defaults, not confirmed by a person</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>36 unresolved material technical/commercial queries: TQ-PRJ-9201-001, TQ-PRJ-9201-002, TQ-PRJ-9201-003, TQ-PRJ-9201-004, TQ-PRJ-9201-005, TQ-PRJ-9201-006</t>
+          <t>estimate approval: no approval record</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1845,15 +1845,125 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>letter of offer: none generated</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Commercial Approver</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>tender-export approval: no approval record</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Commercial Approver</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>reconciliation gate blocked by 50 finding(s)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Commercial Approver</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>estimate state is 'Preliminary — Incomplete'</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Commercial Approver</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>40 unresolved material technical/commercial queries: TQ-PRJ-9201-001, TQ-PRJ-9201-002, TQ-PRJ-9201-003, TQ-PRJ-9201-004, TQ-PRJ-9201-005, TQ-PRJ-9201-006</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Commercial Approver</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>required tender document(s) not received: ITT-CONTRACT, DWG-ARCH-SET, DWG-MEP, DWG-STR-COLUMN, DWG-STR-FOOTING, DWG-STR-SLABBEAM, DWG-STR-STAIR, BBS-REINF, SPEC-ARCH, SPEC-STRUCT, DWG-SITE-LEVELS</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Commercial Approver</t>
         </is>
